--- a/测试数据.xlsx
+++ b/测试数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\F\ABlueFaceProj\20240618\Seg\Beta_BiSeNet-master_Slim\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B34A3CFC-3ED4-4C11-87E4-B7AB66089684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69FC1180-306E-46E9-9026-9887786F93AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="154">
   <si>
     <t>x2</t>
   </si>
@@ -462,14 +462,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>fastefficientbisenet_inceptionnext_atto</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.754584/0.760426</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>0.772044/0.777559</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -511,6 +503,10 @@
   </si>
   <si>
     <t>fastefficientbisenet_cpubone_nano_reparam</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fastefficientbisenet_inceptionnext_atto、sppf</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -978,7 +974,7 @@
         <v>4</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="K1" s="6" t="s">
         <v>137</v>
@@ -990,7 +986,7 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B2">
         <v>0.78639000000000003</v>
@@ -1008,12 +1004,12 @@
         <v>10.33</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B3" s="1">
         <v>0.78566499999999995</v>
@@ -1033,7 +1029,7 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B4" s="1">
         <v>0.78243600000000002</v>
@@ -1138,7 +1134,7 @@
         <v>0.76847900000000002</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H8" s="1">
         <v>0.76789700000000005</v>
@@ -1560,7 +1556,7 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="B28" s="1">
         <v>0.74468699999999999</v>
@@ -1577,8 +1573,8 @@
       <c r="F28" s="1">
         <v>0.75131099999999995</v>
       </c>
-      <c r="G28" s="7" t="s">
-        <v>143</v>
+      <c r="G28" s="7">
+        <v>0.76597599999999999</v>
       </c>
       <c r="H28" s="1">
         <v>0.76078100000000004</v>
@@ -1838,7 +1834,7 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B40" s="1">
         <v>0.73680000000000001</v>
@@ -2140,7 +2136,7 @@
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="13" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B55" s="1">
         <v>0.71189999999999998</v>
@@ -2214,7 +2210,7 @@
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B59" s="1">
         <v>0.69976499999999997</v>
@@ -2291,7 +2287,7 @@
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="9" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="H62">
         <v>0.74091399999999996</v>
@@ -2302,10 +2298,10 @@
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="H63">
-        <v>0.72148599999999996</v>
+        <v>0.72748599999999997</v>
       </c>
       <c r="J63">
         <v>1.73</v>
